--- a/output_6a.xlsx
+++ b/output_6a.xlsx
@@ -1052,7 +1052,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
         <v>-0</v>
@@ -1061,7 +1061,7 @@
         <v>-0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>-0</v>
@@ -1072,7 +1072,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
         <v>-0</v>
@@ -1081,7 +1081,7 @@
         <v>-0</v>
       </c>
       <c r="E12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>-0</v>
@@ -1112,7 +1112,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>-0</v>
@@ -1121,7 +1121,7 @@
         <v>-0</v>
       </c>
       <c r="E14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>-0</v>
@@ -1192,7 +1192,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
         <v>-0</v>
@@ -1201,7 +1201,7 @@
         <v>-0</v>
       </c>
       <c r="E18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
         <v>-0</v>
@@ -1255,16 +1255,16 @@
         <v>-0</v>
       </c>
       <c r="C21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>-0</v>
       </c>
       <c r="F21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
